--- a/inst/extdata/montana_criteria_crosswalk.xlsx
+++ b/inst/extdata/montana_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/k_salkgundersen_tetratech_com/Documents/EPA/R8_AssessmentTool/5_Work/Crosswalks/individual_criteria_crosswalks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9D392EC-D308-45C4-B4D4-DAA83AAE6223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0D095B-CC24-482F-883C-FCD4FE862E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -230,9 +230,6 @@
     <t>arithmetic max average</t>
   </si>
   <si>
-    <t>Anatoxin-a</t>
-  </si>
-  <si>
     <t>Primary Contact Recreation</t>
   </si>
   <si>
@@ -275,15 +272,9 @@
     <t>CADMIUM</t>
   </si>
   <si>
-    <t>Chromium (VI)</t>
-  </si>
-  <si>
     <t>CHROMIUM(VI)</t>
   </si>
   <si>
-    <t>Chromium (III)</t>
-  </si>
-  <si>
     <t>CHROMIUM(III)</t>
   </si>
   <si>
@@ -299,9 +290,6 @@
     <t>CYLINDROSPERMOPSIN</t>
   </si>
   <si>
-    <t>E. coli</t>
-  </si>
-  <si>
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
@@ -341,9 +329,6 @@
     <t>LEAD</t>
   </si>
   <si>
-    <t>Microcystin</t>
-  </si>
-  <si>
     <t>MICROCYSTIN</t>
   </si>
   <si>
@@ -371,9 +356,6 @@
     <t>NITRATE</t>
   </si>
   <si>
-    <t>Oxygen</t>
-  </si>
-  <si>
     <t>DISSOLVED OXYGEN (DO)</t>
   </si>
   <si>
@@ -407,9 +389,6 @@
     <t>early life stages present -  - burbot present</t>
   </si>
   <si>
-    <t>Secchi Depth</t>
-  </si>
-  <si>
     <t>DEPTH, SECCHI DISK DEPTH</t>
   </si>
   <si>
@@ -468,6 +447,27 @@
   </si>
   <si>
     <t>ZINC</t>
+  </si>
+  <si>
+    <t>ESCHERICHIA COLI (E. COLI)</t>
+  </si>
+  <si>
+    <t>CYANOBACTERIA HEPATOTOXIC MICROCYSTINS</t>
+  </si>
+  <si>
+    <t>DISSOLVED OXYGEN</t>
+  </si>
+  <si>
+    <t>CYANOBACTERIA NEUROTOXIC ANATOXINS</t>
+  </si>
+  <si>
+    <t>CHROMIUM, HEXAVALENT</t>
+  </si>
+  <si>
+    <t>CHROMIUM, TRIVALENT, TOTAL</t>
+  </si>
+  <si>
+    <t>SECCHI DISK TRANSPARENCY</t>
   </si>
 </sst>
 </file>
@@ -877,9 +877,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C39393-A058-421C-ACEB-02156F4251A2}">
   <dimension ref="A1:AQ78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:43" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1081,7 +1081,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1152,7 +1152,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1223,7 +1223,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1294,7 +1294,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -1365,7 +1365,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -1436,7 +1436,7 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
@@ -1507,7 +1507,7 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
@@ -1578,19 +1578,19 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -1618,7 +1618,7 @@
         <v>61</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T10" s="5">
         <v>1</v>
@@ -1630,7 +1630,7 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
@@ -1647,22 +1647,22 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
@@ -1718,22 +1718,22 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
@@ -1789,22 +1789,22 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -1831,7 +1831,7 @@
         <v>61</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T13" s="5">
         <v>1</v>
@@ -1858,22 +1858,22 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -1900,7 +1900,7 @@
         <v>61</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T14" s="5">
         <v>1</v>
@@ -1927,22 +1927,22 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="F15" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -1969,7 +1969,7 @@
         <v>61</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T15" s="5">
         <v>1</v>
@@ -1996,22 +1996,22 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
@@ -2067,22 +2067,22 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
@@ -2138,22 +2138,22 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="F18" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -2180,7 +2180,7 @@
         <v>61</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T18" s="5">
         <v>1</v>
@@ -2207,22 +2207,22 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
@@ -2278,22 +2278,22 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
@@ -2349,22 +2349,22 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
@@ -2420,22 +2420,22 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
@@ -2491,22 +2491,22 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
@@ -2562,22 +2562,22 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
@@ -2633,22 +2633,22 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -2675,7 +2675,7 @@
         <v>61</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T25" s="5">
         <v>1</v>
@@ -2702,19 +2702,19 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -2769,19 +2769,19 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>50</v>
@@ -2802,7 +2802,7 @@
         <v>32</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q27" s="5">
         <v>30</v>
@@ -2811,7 +2811,7 @@
         <v>61</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T27" s="5">
         <v>1</v>
@@ -2838,19 +2838,19 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>50</v>
@@ -2871,7 +2871,7 @@
         <v>64</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q28" s="5">
         <v>1</v>
@@ -2880,7 +2880,7 @@
         <v>61</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T28" s="5">
         <v>10</v>
@@ -2907,19 +2907,19 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>50</v>
@@ -2940,7 +2940,7 @@
         <v>126</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q29" s="5">
         <v>30</v>
@@ -2949,7 +2949,7 @@
         <v>61</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T29" s="5">
         <v>1</v>
@@ -2961,7 +2961,7 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
@@ -2978,19 +2978,19 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>50</v>
@@ -3011,7 +3011,7 @@
         <v>252</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q30" s="5">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>61</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T30" s="5">
         <v>10</v>
@@ -3032,7 +3032,7 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Z30" s="5"/>
       <c r="AA30" s="5"/>
@@ -3049,19 +3049,19 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>50</v>
@@ -3082,7 +3082,7 @@
         <v>630</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q31" s="5">
         <v>30</v>
@@ -3091,7 +3091,7 @@
         <v>61</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T31" s="5">
         <v>1</v>
@@ -3103,7 +3103,7 @@
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="Z31" s="5"/>
       <c r="AA31" s="5"/>
@@ -3120,19 +3120,19 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>50</v>
@@ -3153,7 +3153,7 @@
         <v>1260</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q32" s="5">
         <v>1</v>
@@ -3162,7 +3162,7 @@
         <v>61</v>
       </c>
       <c r="S32" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T32" s="5">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
       <c r="Y32" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="Z32" s="5"/>
       <c r="AA32" s="5"/>
@@ -3191,19 +3191,19 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>50</v>
@@ -3224,7 +3224,7 @@
         <v>126</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q33" s="5">
         <v>30</v>
@@ -3233,7 +3233,7 @@
         <v>61</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T33" s="5">
         <v>1</v>
@@ -3245,7 +3245,7 @@
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
       <c r="Y33" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Z33" s="5"/>
       <c r="AA33" s="5"/>
@@ -3262,19 +3262,19 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>50</v>
@@ -3295,7 +3295,7 @@
         <v>252</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q34" s="5">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         <v>61</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T34" s="5">
         <v>10</v>
@@ -3316,7 +3316,7 @@
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
       <c r="Y34" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Z34" s="5"/>
       <c r="AA34" s="5"/>
@@ -3333,19 +3333,19 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>50</v>
@@ -3366,7 +3366,7 @@
         <v>630</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q35" s="5">
         <v>30</v>
@@ -3375,7 +3375,7 @@
         <v>61</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T35" s="5">
         <v>1</v>
@@ -3402,19 +3402,19 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>50</v>
@@ -3435,7 +3435,7 @@
         <v>1260</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q36" s="5">
         <v>1</v>
@@ -3444,7 +3444,7 @@
         <v>61</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T36" s="5">
         <v>10</v>
@@ -3471,19 +3471,19 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -3502,7 +3502,7 @@
         <v>126</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q37" s="5">
         <v>30</v>
@@ -3511,7 +3511,7 @@
         <v>61</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T37" s="5">
         <v>1</v>
@@ -3523,7 +3523,7 @@
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Z37" s="5"/>
       <c r="AA37" s="5"/>
@@ -3540,19 +3540,19 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>50</v>
@@ -3573,7 +3573,7 @@
         <v>252</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q38" s="5">
         <v>30</v>
@@ -3582,7 +3582,7 @@
         <v>61</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="T38" s="5">
         <v>1</v>
@@ -3594,7 +3594,7 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
       <c r="Y38" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Z38" s="5"/>
       <c r="AA38" s="5"/>
@@ -3611,22 +3611,22 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
@@ -3682,22 +3682,22 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
@@ -3753,22 +3753,22 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
@@ -3797,7 +3797,7 @@
         <v>61</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T41" s="5">
         <v>10</v>
@@ -3824,22 +3824,22 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -3866,7 +3866,7 @@
         <v>61</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T42" s="5">
         <v>1</v>
@@ -3893,19 +3893,19 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -3960,22 +3960,22 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5" t="s">
@@ -4031,22 +4031,22 @@
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
@@ -4075,7 +4075,7 @@
         <v>61</v>
       </c>
       <c r="S45" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T45" s="5">
         <v>10</v>
@@ -4102,22 +4102,22 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4171,22 +4171,22 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
@@ -4242,22 +4242,22 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
@@ -4313,22 +4313,22 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4355,7 +4355,7 @@
         <v>61</v>
       </c>
       <c r="S49" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T49" s="5">
         <v>1</v>
@@ -4382,19 +4382,19 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -4422,7 +4422,7 @@
         <v>61</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T50" s="5">
         <v>1</v>
@@ -4449,19 +4449,19 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
     </row>
-    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -4489,7 +4489,7 @@
         <v>61</v>
       </c>
       <c r="S51" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T51" s="5">
         <v>1</v>
@@ -4516,22 +4516,22 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
     </row>
-    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M52" s="5" t="s">
         <v>50</v>
@@ -4587,22 +4587,22 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
     </row>
-    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M53" s="5" t="s">
         <v>50</v>
@@ -4658,22 +4658,22 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
     </row>
-    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>50</v>
@@ -4702,7 +4702,7 @@
         <v>61</v>
       </c>
       <c r="S54" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="T54" s="5">
         <v>1</v>
@@ -4729,22 +4729,22 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
     </row>
-    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>50</v>
@@ -4773,7 +4773,7 @@
         <v>61</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="T55" s="5">
         <v>1</v>
@@ -4800,22 +4800,22 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
     </row>
-    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>50</v>
@@ -4844,7 +4844,7 @@
         <v>61</v>
       </c>
       <c r="S56" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="T56" s="5">
         <v>1</v>
@@ -4871,22 +4871,22 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
     </row>
-    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>50</v>
@@ -4942,22 +4942,22 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
     </row>
-    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>50</v>
@@ -4998,7 +4998,7 @@
       <c r="W58" s="5"/>
       <c r="X58" s="5"/>
       <c r="Y58" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Z58" s="5"/>
       <c r="AA58" s="5"/>
@@ -5015,22 +5015,22 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
     </row>
-    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>50</v>
@@ -5071,7 +5071,7 @@
       <c r="W59" s="5"/>
       <c r="X59" s="5"/>
       <c r="Y59" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
@@ -5088,22 +5088,22 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
     </row>
-    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>50</v>
@@ -5132,7 +5132,7 @@
         <v>61</v>
       </c>
       <c r="S60" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="T60" s="5">
         <v>1</v>
@@ -5159,22 +5159,22 @@
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
     </row>
-    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>50</v>
@@ -5203,7 +5203,7 @@
         <v>61</v>
       </c>
       <c r="S61" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="T61" s="5">
         <v>1</v>
@@ -5215,7 +5215,7 @@
       <c r="W61" s="5"/>
       <c r="X61" s="5"/>
       <c r="Y61" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Z61" s="5"/>
       <c r="AA61" s="5"/>
@@ -5232,22 +5232,22 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
     </row>
-    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>50</v>
@@ -5276,7 +5276,7 @@
         <v>61</v>
       </c>
       <c r="S62" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="T62" s="5">
         <v>1</v>
@@ -5288,7 +5288,7 @@
       <c r="W62" s="5"/>
       <c r="X62" s="5"/>
       <c r="Y62" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Z62" s="5"/>
       <c r="AA62" s="5"/>
@@ -5305,22 +5305,22 @@
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
     </row>
-    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>50</v>
@@ -5349,7 +5349,7 @@
         <v>61</v>
       </c>
       <c r="S63" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="T63" s="5">
         <v>1</v>
@@ -5376,32 +5376,32 @@
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
     </row>
-    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>49</v>
       </c>
       <c r="K64" s="5"/>
       <c r="L64" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>50</v>
@@ -5411,13 +5411,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="Q64" s="5">
         <v>1</v>
       </c>
       <c r="R64" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="S64" s="5" t="s">
         <v>53</v>
@@ -5432,7 +5432,7 @@
       <c r="W64" s="5"/>
       <c r="X64" s="5"/>
       <c r="Y64" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="Z64" s="5"/>
       <c r="AA64" s="5"/>
@@ -5449,32 +5449,32 @@
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
     </row>
-    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>49</v>
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>50</v>
@@ -5484,13 +5484,13 @@
         <v>2</v>
       </c>
       <c r="P65" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="Q65" s="5">
         <v>1</v>
       </c>
       <c r="R65" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="S65" s="5" t="s">
         <v>53</v>
@@ -5505,7 +5505,7 @@
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
       <c r="Y65" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="Z65" s="5"/>
       <c r="AA65" s="5"/>
@@ -5522,32 +5522,32 @@
       <c r="AL65" s="5"/>
       <c r="AM65" s="5"/>
     </row>
-    <row r="66" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>49</v>
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>50</v>
@@ -5557,13 +5557,13 @@
         <v>1</v>
       </c>
       <c r="P66" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="Q66" s="5">
         <v>1</v>
       </c>
       <c r="R66" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="S66" s="5" t="s">
         <v>53</v>
@@ -5578,7 +5578,7 @@
       <c r="W66" s="5"/>
       <c r="X66" s="5"/>
       <c r="Y66" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="Z66" s="5"/>
       <c r="AA66" s="5"/>
@@ -5595,32 +5595,32 @@
       <c r="AL66" s="5"/>
       <c r="AM66" s="5"/>
     </row>
-    <row r="67" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>49</v>
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="M67" s="5" t="s">
         <v>50</v>
@@ -5630,13 +5630,13 @@
         <v>1</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="Q67" s="5">
         <v>1</v>
       </c>
       <c r="R67" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="S67" s="5" t="s">
         <v>53</v>
@@ -5651,7 +5651,7 @@
       <c r="W67" s="5"/>
       <c r="X67" s="5"/>
       <c r="Y67" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="Z67" s="5"/>
       <c r="AA67" s="5"/>
@@ -5668,22 +5668,22 @@
       <c r="AL67" s="5"/>
       <c r="AM67" s="5"/>
     </row>
-    <row r="68" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5" t="s">
@@ -5739,22 +5739,22 @@
       <c r="AL68" s="5"/>
       <c r="AM68" s="5"/>
     </row>
-    <row r="69" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
@@ -5810,22 +5810,22 @@
       <c r="AL69" s="5"/>
       <c r="AM69" s="5"/>
     </row>
-    <row r="70" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5852,7 +5852,7 @@
         <v>61</v>
       </c>
       <c r="S70" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T70" s="5">
         <v>1</v>
@@ -5879,22 +5879,22 @@
       <c r="AL70" s="5"/>
       <c r="AM70" s="5"/>
     </row>
-    <row r="71" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5" t="s">
@@ -5950,22 +5950,22 @@
       <c r="AL71" s="5"/>
       <c r="AM71" s="5"/>
     </row>
-    <row r="72" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5992,7 +5992,7 @@
         <v>61</v>
       </c>
       <c r="S72" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T72" s="5">
         <v>1</v>
@@ -6019,22 +6019,22 @@
       <c r="AL72" s="5"/>
       <c r="AM72" s="5"/>
     </row>
-    <row r="73" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -6061,7 +6061,7 @@
         <v>61</v>
       </c>
       <c r="S73" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T73" s="5">
         <v>1</v>
@@ -6088,22 +6088,22 @@
       <c r="AL73" s="5"/>
       <c r="AM73" s="5"/>
     </row>
-    <row r="74" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -6130,7 +6130,7 @@
         <v>61</v>
       </c>
       <c r="S74" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T74" s="5">
         <v>1</v>
@@ -6157,22 +6157,22 @@
       <c r="AL74" s="5"/>
       <c r="AM74" s="5"/>
     </row>
-    <row r="75" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -6199,7 +6199,7 @@
         <v>61</v>
       </c>
       <c r="S75" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T75" s="5">
         <v>1</v>
@@ -6226,22 +6226,22 @@
       <c r="AL75" s="5"/>
       <c r="AM75" s="5"/>
     </row>
-    <row r="76" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5" t="s">
@@ -6297,22 +6297,22 @@
       <c r="AL76" s="5"/>
       <c r="AM76" s="5"/>
     </row>
-    <row r="77" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5" t="s">
@@ -6368,22 +6368,22 @@
       <c r="AL77" s="5"/>
       <c r="AM77" s="5"/>
     </row>
-    <row r="78" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -6410,7 +6410,7 @@
         <v>61</v>
       </c>
       <c r="S78" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T78" s="5">
         <v>1</v>

--- a/inst/extdata/montana_criteria_crosswalk.xlsx
+++ b/inst/extdata/montana_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{7C0D095B-CC24-482F-883C-FCD4FE862E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5011EAF-6259-441A-8D6F-E6E2CA56DECD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DE83F6-A026-4B0F-B0F7-EE18FBA9E02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -287,9 +287,6 @@
     <t>Classes A-1 and A-closed</t>
   </si>
   <si>
-    <t>#/100mL</t>
-  </si>
-  <si>
     <t>geometric mean</t>
   </si>
   <si>
@@ -377,9 +374,6 @@
     <t>Mountain Level III Ecoregions</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>n-month</t>
   </si>
   <si>
@@ -528,6 +522,12 @@
   </si>
   <si>
     <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688))))*(1.45*10^(0.028*(25-max(Temperature, 7))))*2.5</t>
+  </si>
+  <si>
+    <t>CFU/100ML</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -940,17 +940,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C39393-A058-421C-ACEB-02156F4251A2}">
   <dimension ref="A1:AP78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="24" width="9.140625" style="5"/>
-    <col min="25" max="25" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="9.140625" style="5"/>
-    <col min="31" max="31" width="25.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="24" width="9.1796875" style="5"/>
+    <col min="25" max="25" width="18.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="9.1796875" style="5"/>
+    <col min="31" max="31" width="25.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -1148,7 +1148,7 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -1218,7 +1218,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>42</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>57</v>
@@ -1280,10 +1280,10 @@
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
@@ -1304,7 +1304,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>42</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>57</v>
@@ -1366,10 +1366,10 @@
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
@@ -1390,7 +1390,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>57</v>
@@ -1452,13 +1452,13 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>57</v>
@@ -1520,13 +1520,13 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>42</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>57</v>
@@ -1588,10 +1588,10 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
@@ -1600,7 +1600,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>42</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>57</v>
@@ -1662,10 +1662,10 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1674,13 +1674,13 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>62</v>
@@ -1726,13 +1726,13 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
@@ -1746,7 +1746,7 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>42</v>
@@ -1816,7 +1816,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>42</v>
@@ -1886,7 +1886,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>42</v>
@@ -1954,7 +1954,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>42</v>
@@ -2022,7 +2022,7 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -2090,7 +2090,7 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -2160,7 +2160,7 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>42</v>
@@ -2230,7 +2230,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -2298,13 +2298,13 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>44</v>
@@ -2368,13 +2368,13 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>44</v>
@@ -2438,13 +2438,13 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>44</v>
@@ -2508,13 +2508,13 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>44</v>
@@ -2578,7 +2578,7 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>42</v>
@@ -2648,7 +2648,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>42</v>
@@ -2718,7 +2718,7 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
@@ -2786,7 +2786,7 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>42</v>
@@ -2852,13 +2852,13 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>68</v>
@@ -2885,7 +2885,7 @@
         <v>32</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
@@ -2894,7 +2894,7 @@
         <v>59</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
@@ -2920,13 +2920,13 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>68</v>
@@ -2953,7 +2953,7 @@
         <v>64</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
@@ -2988,13 +2988,13 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>62</v>
@@ -3021,7 +3021,7 @@
         <v>126</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q29" s="3">
         <v>30</v>
@@ -3030,7 +3030,7 @@
         <v>59</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
@@ -3042,13 +3042,13 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA29" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="AA29" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -3062,13 +3062,13 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>62</v>
@@ -3095,7 +3095,7 @@
         <v>252</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
@@ -3116,13 +3116,13 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA30" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="AA30" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
@@ -3136,16 +3136,16 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>81</v>
@@ -3169,7 +3169,7 @@
         <v>630</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
@@ -3178,7 +3178,7 @@
         <v>59</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
@@ -3190,13 +3190,13 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z31" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA31" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="AA31" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
@@ -3210,16 +3210,16 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>81</v>
@@ -3243,7 +3243,7 @@
         <v>1260</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
@@ -3264,13 +3264,13 @@
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z32" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA32" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="AA32" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
@@ -3284,13 +3284,13 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>62</v>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>49</v>
@@ -3317,7 +3317,7 @@
         <v>126</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q33" s="3">
         <v>30</v>
@@ -3326,7 +3326,7 @@
         <v>59</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
@@ -3338,13 +3338,13 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z33" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA33" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="AA33" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
@@ -3358,13 +3358,13 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>62</v>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>49</v>
@@ -3391,7 +3391,7 @@
         <v>252</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
@@ -3412,13 +3412,13 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA34" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="AA34" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
@@ -3432,16 +3432,16 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>81</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>49</v>
@@ -3465,7 +3465,7 @@
         <v>630</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q35" s="3">
         <v>30</v>
@@ -3474,7 +3474,7 @@
         <v>59</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
@@ -3500,16 +3500,16 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>81</v>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>49</v>
@@ -3533,7 +3533,7 @@
         <v>1260</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
@@ -3568,16 +3568,16 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>81</v>
@@ -3599,7 +3599,7 @@
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
@@ -3608,7 +3608,7 @@
         <v>59</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
@@ -3620,13 +3620,13 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA37" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="AA37" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3640,16 +3640,16 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>81</v>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>49</v>
@@ -3673,7 +3673,7 @@
         <v>252</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
@@ -3682,7 +3682,7 @@
         <v>59</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
@@ -3694,13 +3694,13 @@
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z38" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA38" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="AA38" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3714,19 +3714,19 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>67</v>
@@ -3784,19 +3784,19 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>67</v>
@@ -3854,19 +3854,19 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>67</v>
@@ -3924,19 +3924,19 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>67</v>
@@ -3992,19 +3992,19 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>62</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -4058,19 +4058,19 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>67</v>
@@ -4128,19 +4128,19 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>67</v>
@@ -4198,19 +4198,19 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>67</v>
@@ -4266,19 +4266,19 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>67</v>
@@ -4336,19 +4336,19 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>67</v>
@@ -4406,19 +4406,19 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>67</v>
@@ -4474,19 +4474,19 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -4540,19 +4540,19 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -4606,22 +4606,22 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>49</v>
@@ -4676,22 +4676,22 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M53" s="3" t="s">
         <v>49</v>
@@ -4746,22 +4746,22 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>49</v>
@@ -4790,7 +4790,7 @@
         <v>59</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
@@ -4816,22 +4816,22 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>49</v>
@@ -4860,7 +4860,7 @@
         <v>59</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
@@ -4886,22 +4886,22 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>49</v>
@@ -4930,7 +4930,7 @@
         <v>59</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
@@ -4956,22 +4956,22 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>49</v>
@@ -5026,22 +5026,22 @@
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
     </row>
-    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>49</v>
@@ -5082,13 +5082,13 @@
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z58" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA58" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
@@ -5102,22 +5102,22 @@
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
     </row>
-    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E59" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>49</v>
@@ -5158,13 +5158,13 @@
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z59" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA59" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
@@ -5178,22 +5178,22 @@
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
     </row>
-    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E60" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>49</v>
@@ -5222,7 +5222,7 @@
         <v>59</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
@@ -5248,22 +5248,22 @@
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
     </row>
-    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E61" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M61" s="3" t="s">
         <v>49</v>
@@ -5292,7 +5292,7 @@
         <v>59</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
@@ -5304,13 +5304,13 @@
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z61" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA61" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
@@ -5324,22 +5324,22 @@
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
     </row>
-    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>49</v>
@@ -5368,7 +5368,7 @@
         <v>59</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T62" s="3">
         <v>1</v>
@@ -5380,13 +5380,13 @@
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z62" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA62" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
@@ -5400,22 +5400,22 @@
       <c r="AK62" s="3"/>
       <c r="AL62" s="3"/>
     </row>
-    <row r="63" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M63" s="3" t="s">
         <v>49</v>
@@ -5444,7 +5444,7 @@
         <v>59</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T63" s="3">
         <v>1</v>
@@ -5470,32 +5470,32 @@
       <c r="AK63" s="3"/>
       <c r="AL63" s="3"/>
     </row>
-    <row r="64" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M64" s="3" t="s">
         <v>49</v>
@@ -5505,13 +5505,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S64" s="3" t="s">
         <v>52</v>
@@ -5526,13 +5526,13 @@
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Z64" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AA64" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
@@ -5546,32 +5546,32 @@
       <c r="AK64" s="3"/>
       <c r="AL64" s="3"/>
     </row>
-    <row r="65" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M65" s="3" t="s">
         <v>49</v>
@@ -5581,13 +5581,13 @@
         <v>2</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S65" s="3" t="s">
         <v>52</v>
@@ -5602,13 +5602,13 @@
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Z65" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AA65" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
@@ -5622,32 +5622,32 @@
       <c r="AK65" s="3"/>
       <c r="AL65" s="3"/>
     </row>
-    <row r="66" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>49</v>
@@ -5657,13 +5657,13 @@
         <v>1</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>52</v>
@@ -5678,13 +5678,13 @@
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Z66" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AA66" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
@@ -5698,32 +5698,32 @@
       <c r="AK66" s="3"/>
       <c r="AL66" s="3"/>
     </row>
-    <row r="67" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M67" s="3" t="s">
         <v>49</v>
@@ -5733,13 +5733,13 @@
         <v>1</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S67" s="3" t="s">
         <v>52</v>
@@ -5754,13 +5754,13 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Z67" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AA67" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
@@ -5774,19 +5774,19 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>67</v>
@@ -5844,19 +5844,19 @@
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
     </row>
-    <row r="69" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>67</v>
@@ -5914,19 +5914,19 @@
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
     </row>
-    <row r="70" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>67</v>
@@ -5982,19 +5982,19 @@
       <c r="AK70" s="3"/>
       <c r="AL70" s="3"/>
     </row>
-    <row r="71" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>67</v>
@@ -6052,19 +6052,19 @@
       <c r="AK71" s="3"/>
       <c r="AL71" s="3"/>
     </row>
-    <row r="72" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>67</v>
@@ -6120,19 +6120,19 @@
       <c r="AK72" s="3"/>
       <c r="AL72" s="3"/>
     </row>
-    <row r="73" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>67</v>
@@ -6188,19 +6188,19 @@
       <c r="AK73" s="3"/>
       <c r="AL73" s="3"/>
     </row>
-    <row r="74" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>67</v>
@@ -6256,19 +6256,19 @@
       <c r="AK74" s="3"/>
       <c r="AL74" s="3"/>
     </row>
-    <row r="75" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>67</v>
@@ -6324,19 +6324,19 @@
       <c r="AK75" s="3"/>
       <c r="AL75" s="3"/>
     </row>
-    <row r="76" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>67</v>
@@ -6394,19 +6394,19 @@
       <c r="AK76" s="3"/>
       <c r="AL76" s="3"/>
     </row>
-    <row r="77" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>67</v>
@@ -6464,19 +6464,19 @@
       <c r="AK77" s="3"/>
       <c r="AL77" s="3"/>
     </row>
-    <row r="78" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>67</v>

--- a/inst/extdata/montana_criteria_crosswalk.xlsx
+++ b/inst/extdata/montana_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DE83F6-A026-4B0F-B0F7-EE18FBA9E02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EF67AA-C36E-4079-ADCD-13CFFD121107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>EquationType</t>
   </si>
   <si>
-    <t>Equation</t>
-  </si>
-  <si>
     <t>hardness_param_1</t>
   </si>
   <si>
@@ -528,6 +525,9 @@
   </si>
   <si>
     <t>M</t>
+  </si>
+  <si>
+    <t>EquationFormula</t>
   </si>
 </sst>
 </file>
@@ -940,17 +940,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C39393-A058-421C-ACEB-02156F4251A2}">
   <dimension ref="A1:AP78"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="24" width="9.1796875" style="5"/>
-    <col min="25" max="25" width="18.26953125" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="9.1796875" style="5"/>
-    <col min="31" max="31" width="25.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.1796875" style="5"/>
+    <col min="1" max="24" width="9.140625" style="5"/>
+    <col min="25" max="25" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="9.140625" style="5"/>
+    <col min="31" max="31" width="25.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,90 +1045,90 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>750</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T2" s="3">
         <v>10</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1148,57 +1148,57 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>87</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q3" s="3">
         <v>96</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T3" s="3">
         <v>10</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1218,57 +1218,57 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T4" s="3">
         <v>10</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1280,10 +1280,10 @@
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
@@ -1304,57 +1304,57 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T5" s="3">
         <v>10</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1366,10 +1366,10 @@
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
@@ -1390,57 +1390,57 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q6" s="3">
         <v>30</v>
       </c>
       <c r="R6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1452,63 +1452,63 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q7" s="3">
         <v>30</v>
       </c>
       <c r="R7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T7" s="3">
-        <v>1</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1520,63 +1520,63 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q8" s="3">
         <v>4</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T8" s="3">
         <v>10</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1588,10 +1588,10 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
@@ -1600,57 +1600,57 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="3">
         <v>4</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T9" s="3">
         <v>10</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1662,10 +1662,10 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1674,65 +1674,65 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3">
         <v>20</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Z10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA10" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
@@ -1746,57 +1746,57 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>340</v>
       </c>
       <c r="P11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q11" s="3">
-        <v>1</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="S11" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T11" s="3">
         <v>10</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1816,57 +1816,57 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>150</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q12" s="3">
         <v>96</v>
       </c>
       <c r="R12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T12" s="3">
         <v>10</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1886,55 +1886,55 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>10</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T13" s="3">
+        <v>1</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1954,55 +1954,55 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3">
         <v>1000</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
       </c>
       <c r="R14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -2022,55 +2022,55 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3">
         <v>4</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -2090,57 +2090,57 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>0.49</v>
       </c>
       <c r="P16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3" t="s">
+      <c r="S16" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T16" s="3">
         <v>10</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2160,57 +2160,57 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>0.25</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q17" s="3">
         <v>96</v>
       </c>
       <c r="R17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T17" s="3">
         <v>10</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2230,55 +2230,55 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>5</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
       </c>
       <c r="R18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2298,57 +2298,57 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>16</v>
       </c>
       <c r="P19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q19" s="3">
-        <v>1</v>
-      </c>
-      <c r="R19" s="3" t="s">
+      <c r="S19" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T19" s="3">
         <v>10</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2368,57 +2368,57 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>11</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q20" s="3">
         <v>96</v>
       </c>
       <c r="R20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T20" s="3">
         <v>10</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2438,57 +2438,57 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3">
         <v>579</v>
       </c>
       <c r="P21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q21" s="3">
-        <v>1</v>
-      </c>
-      <c r="R21" s="3" t="s">
+      <c r="S21" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T21" s="3">
         <v>10</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2508,57 +2508,57 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3">
         <v>27.7</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q22" s="3">
         <v>96</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T22" s="3">
         <v>10</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2578,57 +2578,57 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>3.79</v>
       </c>
       <c r="P23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q23" s="3">
-        <v>1</v>
-      </c>
-      <c r="R23" s="3" t="s">
+      <c r="S23" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T23" s="3">
         <v>10</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2648,57 +2648,57 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>2.85</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q24" s="3">
         <v>96</v>
       </c>
       <c r="R24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S24" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T24" s="3">
         <v>10</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2718,55 +2718,55 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>1300</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q25" s="3">
         <v>1</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T25" s="3">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T25" s="3">
-        <v>1</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2786,53 +2786,53 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>15</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2852,55 +2852,55 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>32</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2920,55 +2920,55 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>64</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T28" s="3">
         <v>10</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2988,67 +2988,67 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>126</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q29" s="3">
         <v>30</v>
       </c>
       <c r="R29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T29" s="3">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T29" s="3">
-        <v>1</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z29" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AA29" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -3062,67 +3062,67 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>252</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T30" s="3">
         <v>10</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z30" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AA30" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
@@ -3136,67 +3136,67 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>630</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T31" s="3">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z31" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AA31" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
@@ -3210,67 +3210,67 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>1260</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T32" s="3">
         <v>10</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z32" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AA32" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
@@ -3284,67 +3284,67 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3">
         <v>126</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q33" s="3">
         <v>30</v>
       </c>
       <c r="R33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1</v>
+      </c>
+      <c r="U33" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z33" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AA33" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
@@ -3358,67 +3358,67 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>252</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T34" s="3">
         <v>10</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AA34" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
@@ -3432,55 +3432,55 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>630</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q35" s="3">
         <v>30</v>
       </c>
       <c r="R35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1</v>
+      </c>
+      <c r="U35" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T35" s="3">
-        <v>1</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3500,55 +3500,55 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>1260</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T36" s="3">
         <v>10</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3568,65 +3568,65 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T37" s="3">
+        <v>1</v>
+      </c>
+      <c r="U37" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T37" s="3">
-        <v>1</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z37" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AA37" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3640,67 +3640,67 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>252</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
       </c>
       <c r="R38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T38" s="3">
+        <v>1</v>
+      </c>
+      <c r="U38" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="T38" s="3">
-        <v>1</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z38" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AA38" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3714,57 +3714,57 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3">
         <v>1000</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q39" s="3">
         <v>96</v>
       </c>
       <c r="R39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S39" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3784,57 +3784,57 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="F40" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>13.98</v>
       </c>
       <c r="P40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1</v>
+      </c>
+      <c r="R40" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q40" s="3">
-        <v>1</v>
-      </c>
-      <c r="R40" s="3" t="s">
+      <c r="S40" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T40" s="3">
         <v>10</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3854,57 +3854,57 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="F41" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>0.54500000000000004</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T41" s="3">
         <v>10</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3924,55 +3924,55 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="F42" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>15</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T42" s="3">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T42" s="3">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3992,53 +3992,53 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>8</v>
       </c>
       <c r="P43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>1</v>
+      </c>
+      <c r="R43" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q43" s="3">
-        <v>1</v>
-      </c>
-      <c r="R43" s="3" t="s">
+      <c r="S43" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -4058,57 +4058,57 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="F44" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>1.7</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q44" s="3">
         <v>96</v>
       </c>
       <c r="R44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T44" s="3">
         <v>10</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -4128,57 +4128,57 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="F45" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>0.91</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T45" s="3">
         <v>10</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4198,55 +4198,55 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>0.05</v>
       </c>
       <c r="P46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>1</v>
+      </c>
+      <c r="R46" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q46" s="3">
-        <v>1</v>
-      </c>
-      <c r="R46" s="3" t="s">
+      <c r="S46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4266,57 +4266,57 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F47" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>145</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q47" s="3">
         <v>96</v>
       </c>
       <c r="R47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S47" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T47" s="3">
         <v>10</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4336,57 +4336,57 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>16.100000000000001</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q48" s="3">
         <v>96</v>
       </c>
       <c r="R48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S48" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T48" s="3">
         <v>10</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4406,55 +4406,55 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F49" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>100</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T49" s="3">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4474,53 +4474,53 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>1</v>
       </c>
       <c r="P50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>1</v>
+      </c>
+      <c r="R50" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q50" s="3">
-        <v>1</v>
-      </c>
-      <c r="R50" s="3" t="s">
+      <c r="S50" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4540,53 +4540,53 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>10</v>
       </c>
       <c r="P51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>1</v>
+      </c>
+      <c r="R51" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q51" s="3">
-        <v>1</v>
-      </c>
-      <c r="R51" s="3" t="s">
+      <c r="S51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T51" s="3">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4606,57 +4606,57 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N52" s="3">
         <v>6.5</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T52" s="3">
+        <v>1</v>
+      </c>
+      <c r="U52" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4676,57 +4676,57 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N53" s="3">
         <v>9.5</v>
       </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q53" s="3">
         <v>7</v>
       </c>
       <c r="R53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T53" s="3">
+        <v>1</v>
+      </c>
+      <c r="U53" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S53" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T53" s="3">
-        <v>1</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4746,57 +4746,57 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E54" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N54" s="3">
         <v>5</v>
       </c>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q54" s="3">
         <v>7</v>
       </c>
       <c r="R54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4816,57 +4816,57 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N55" s="3">
         <v>8</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>1</v>
+      </c>
+      <c r="R55" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q55" s="3">
-        <v>1</v>
-      </c>
-      <c r="R55" s="3" t="s">
+      <c r="S55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T55" s="3">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T55" s="3">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4886,57 +4886,57 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N56" s="3">
         <v>4</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>1</v>
+      </c>
+      <c r="R56" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q56" s="3">
-        <v>1</v>
-      </c>
-      <c r="R56" s="3" t="s">
+      <c r="S56" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T56" s="3">
+        <v>1</v>
+      </c>
+      <c r="U56" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T56" s="3">
-        <v>1</v>
-      </c>
-      <c r="U56" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4956,57 +4956,57 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E57" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N57" s="3">
         <v>5.5</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q57" s="3">
         <v>30</v>
       </c>
       <c r="R57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T57" s="3">
+        <v>1</v>
+      </c>
+      <c r="U57" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -5026,69 +5026,69 @@
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
     </row>
-    <row r="58" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E58" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N58" s="3">
         <v>6</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q58" s="3">
         <v>7</v>
       </c>
       <c r="R58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T58" s="3">
+        <v>1</v>
+      </c>
+      <c r="U58" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T58" s="3">
-        <v>1</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Z58" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA58" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="AA58" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
@@ -5102,69 +5102,69 @@
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
     </row>
-    <row r="59" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E59" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N59" s="3">
         <v>6</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q59" s="3">
         <v>7</v>
       </c>
       <c r="R59" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T59" s="3">
+        <v>1</v>
+      </c>
+      <c r="U59" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z59" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AA59" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
@@ -5178,57 +5178,57 @@
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
     </row>
-    <row r="60" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E60" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N60" s="3">
         <v>4</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q60" s="3">
         <v>7</v>
       </c>
       <c r="R60" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="T60" s="3">
+        <v>1</v>
+      </c>
+      <c r="U60" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
@@ -5248,69 +5248,69 @@
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
     </row>
-    <row r="61" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N61" s="3">
         <v>5</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>1</v>
+      </c>
+      <c r="R61" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q61" s="3">
-        <v>1</v>
-      </c>
-      <c r="R61" s="3" t="s">
+      <c r="S61" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T61" s="3">
+        <v>1</v>
+      </c>
+      <c r="U61" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S61" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T61" s="3">
-        <v>1</v>
-      </c>
-      <c r="U61" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Z61" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA61" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="AA61" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
@@ -5324,69 +5324,69 @@
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
     </row>
-    <row r="62" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E62" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N62" s="3">
         <v>5</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1</v>
+      </c>
+      <c r="R62" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q62" s="3">
-        <v>1</v>
-      </c>
-      <c r="R62" s="3" t="s">
+      <c r="S62" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T62" s="3">
+        <v>1</v>
+      </c>
+      <c r="U62" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z62" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AA62" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
@@ -5400,57 +5400,57 @@
       <c r="AK62" s="3"/>
       <c r="AL62" s="3"/>
     </row>
-    <row r="63" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E63" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N63" s="3">
         <v>3</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>1</v>
+      </c>
+      <c r="R63" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q63" s="3">
-        <v>1</v>
-      </c>
-      <c r="R63" s="3" t="s">
+      <c r="S63" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T63" s="3">
+        <v>1</v>
+      </c>
+      <c r="U63" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S63" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T63" s="3">
-        <v>1</v>
-      </c>
-      <c r="U63" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
@@ -5470,69 +5470,69 @@
       <c r="AK63" s="3"/>
       <c r="AL63" s="3"/>
     </row>
-    <row r="64" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N64" s="3"/>
       <c r="O64" s="3">
         <v>2</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T64" s="3">
         <v>1</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z64" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA64" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
@@ -5546,69 +5546,69 @@
       <c r="AK64" s="3"/>
       <c r="AL64" s="3"/>
     </row>
-    <row r="65" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" s="3">
         <v>2</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T65" s="3">
         <v>1</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z65" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA65" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
@@ -5622,69 +5622,69 @@
       <c r="AK65" s="3"/>
       <c r="AL65" s="3"/>
     </row>
-    <row r="66" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3">
         <v>1</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T66" s="3">
         <v>1</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z66" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA66" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
@@ -5698,69 +5698,69 @@
       <c r="AK66" s="3"/>
       <c r="AL66" s="3"/>
     </row>
-    <row r="67" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3">
         <v>1</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T67" s="3">
         <v>1</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z67" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA67" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
@@ -5774,57 +5774,57 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="F68" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3">
         <v>20</v>
       </c>
       <c r="P68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>1</v>
+      </c>
+      <c r="R68" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q68" s="3">
-        <v>1</v>
-      </c>
-      <c r="R68" s="3" t="s">
+      <c r="S68" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T68" s="3">
         <v>10</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
@@ -5844,57 +5844,57 @@
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
     </row>
-    <row r="69" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="F69" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3">
         <v>5</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q69" s="3">
         <v>96</v>
       </c>
       <c r="R69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S69" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T69" s="3">
         <v>10</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
@@ -5914,55 +5914,55 @@
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
     </row>
-    <row r="70" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="F70" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="3">
         <v>50</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q70" s="3">
         <v>1</v>
       </c>
       <c r="R70" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T70" s="3">
+        <v>1</v>
+      </c>
+      <c r="U70" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T70" s="3">
-        <v>1</v>
-      </c>
-      <c r="U70" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -5982,57 +5982,57 @@
       <c r="AK70" s="3"/>
       <c r="AL70" s="3"/>
     </row>
-    <row r="71" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F71" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3">
         <v>0.374</v>
       </c>
       <c r="P71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>1</v>
+      </c>
+      <c r="R71" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q71" s="3">
-        <v>1</v>
-      </c>
-      <c r="R71" s="3" t="s">
+      <c r="S71" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S71" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="T71" s="3">
         <v>1</v>
       </c>
       <c r="U71" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6052,55 +6052,55 @@
       <c r="AK71" s="3"/>
       <c r="AL71" s="3"/>
     </row>
-    <row r="72" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F72" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="3">
         <v>100</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q72" s="3">
         <v>1</v>
       </c>
       <c r="R72" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T72" s="3">
+        <v>1</v>
+      </c>
+      <c r="U72" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T72" s="3">
-        <v>1</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
@@ -6120,55 +6120,55 @@
       <c r="AK72" s="3"/>
       <c r="AL72" s="3"/>
     </row>
-    <row r="73" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="F73" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N73" s="3"/>
       <c r="O73" s="3">
         <v>4000</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q73" s="3">
         <v>1</v>
       </c>
       <c r="R73" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S73" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T73" s="3">
+        <v>1</v>
+      </c>
+      <c r="U73" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S73" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T73" s="3">
-        <v>1</v>
-      </c>
-      <c r="U73" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
@@ -6188,55 +6188,55 @@
       <c r="AK73" s="3"/>
       <c r="AL73" s="3"/>
     </row>
-    <row r="74" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="F74" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="3">
         <v>0.24</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q74" s="3">
         <v>1</v>
       </c>
       <c r="R74" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S74" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T74" s="3">
+        <v>1</v>
+      </c>
+      <c r="U74" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T74" s="3">
-        <v>1</v>
-      </c>
-      <c r="U74" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
@@ -6256,55 +6256,55 @@
       <c r="AK74" s="3"/>
       <c r="AL74" s="3"/>
     </row>
-    <row r="75" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="F75" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" s="3">
         <v>30</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
       </c>
       <c r="R75" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S75" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T75" s="3">
+        <v>1</v>
+      </c>
+      <c r="U75" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T75" s="3">
-        <v>1</v>
-      </c>
-      <c r="U75" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
@@ -6324,57 +6324,57 @@
       <c r="AK75" s="3"/>
       <c r="AL75" s="3"/>
     </row>
-    <row r="76" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="F76" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" s="3">
         <v>37</v>
       </c>
       <c r="P76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>1</v>
+      </c>
+      <c r="R76" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q76" s="3">
-        <v>1</v>
-      </c>
-      <c r="R76" s="3" t="s">
+      <c r="S76" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T76" s="3">
         <v>10</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
@@ -6394,57 +6394,57 @@
       <c r="AK76" s="3"/>
       <c r="AL76" s="3"/>
     </row>
-    <row r="77" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="F77" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N77" s="3"/>
       <c r="O77" s="3">
         <v>37</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q77" s="3">
         <v>96</v>
       </c>
       <c r="R77" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S77" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S77" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T77" s="3">
         <v>10</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
@@ -6464,55 +6464,55 @@
       <c r="AK77" s="3"/>
       <c r="AL77" s="3"/>
     </row>
-    <row r="78" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="F78" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" s="3">
         <v>7400</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q78" s="3">
         <v>1</v>
       </c>
       <c r="R78" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T78" s="3">
+        <v>1</v>
+      </c>
+      <c r="U78" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="S78" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T78" s="3">
-        <v>1</v>
-      </c>
-      <c r="U78" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>

--- a/inst/extdata/montana_criteria_crosswalk.xlsx
+++ b/inst/extdata/montana_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EF67AA-C36E-4079-ADCD-13CFFD121107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{A9EF67AA-C36E-4079-ADCD-13CFFD121107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894F2CA2-1D0E-4B1B-A280-E513EFBD4E09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="174">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -143,12 +143,6 @@
     <t>hardness_param_4</t>
   </si>
   <si>
-    <t>hardness_param_5</t>
-  </si>
-  <si>
-    <t>hardness_param_6</t>
-  </si>
-  <si>
     <t>pH_param_1</t>
   </si>
   <si>
@@ -527,14 +521,50 @@
     <t>M</t>
   </si>
   <si>
-    <t>EquationFormula</t>
+    <t>Equation</t>
+  </si>
+  <si>
+    <t>pHThreshold</t>
+  </si>
+  <si>
+    <t>pHDirection</t>
+  </si>
+  <si>
+    <t>TemperatureExtreme</t>
+  </si>
+  <si>
+    <t>MinEqMagnitude</t>
+  </si>
+  <si>
+    <t>MaxEqMagnitude</t>
+  </si>
+  <si>
+    <t>pH_param_5</t>
+  </si>
+  <si>
+    <t>pH_param_6</t>
+  </si>
+  <si>
+    <t>pH_param_7</t>
+  </si>
+  <si>
+    <t>pH_param_8</t>
+  </si>
+  <si>
+    <t>pH_param_9</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,6 +597,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -588,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -603,6 +640,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -939,18 +979,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C39393-A058-421C-ACEB-02156F4251A2}">
-  <dimension ref="A1:AP78"/>
+  <dimension ref="A1:AX78"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="24" width="9.140625" style="5"/>
     <col min="25" max="25" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="26" max="30" width="9.140625" style="5"/>
     <col min="31" max="31" width="25.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="5"/>
+    <col min="32" max="32" width="110.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,90 +1089,114 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AR1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW1" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AX1" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>750</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T2" s="3">
         <v>10</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1147,58 +1215,59 @@
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
-    </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="3"/>
+    </row>
+    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>87</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="3">
         <v>96</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T3" s="3">
         <v>10</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1217,58 +1286,59 @@
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
-    </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM3" s="3"/>
+    </row>
+    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T4" s="3">
         <v>10</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1280,10 +1350,10 @@
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
@@ -1291,70 +1361,71 @@
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
-      <c r="AM4" s="5">
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="5">
         <v>0.27500000000000002</v>
       </c>
-      <c r="AN4" s="5">
+      <c r="AO4" s="5">
         <v>7.2039999999999997</v>
       </c>
-      <c r="AO4" s="5">
-        <v>39</v>
-      </c>
       <c r="AP4" s="5">
+        <v>39</v>
+      </c>
+      <c r="AQ4" s="5">
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T5" s="3">
         <v>10</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1366,10 +1437,10 @@
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
@@ -1377,70 +1448,71 @@
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
-      <c r="AM5" s="5">
+      <c r="AM5" s="3"/>
+      <c r="AN5" s="5">
         <v>0.41099999999999998</v>
       </c>
-      <c r="AN5" s="5">
+      <c r="AO5" s="5">
         <v>7.2039999999999997</v>
       </c>
-      <c r="AO5" s="5">
+      <c r="AP5" s="5">
         <v>58.4</v>
       </c>
-      <c r="AP5" s="5">
+      <c r="AQ5" s="5">
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q6" s="3">
         <v>30</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T6" s="3">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1452,63 +1524,95 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AM6" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AN6" s="5">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="AO6" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP6" s="5">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="AQ6" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR6" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="AS6" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="AT6" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="AU6" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AV6" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="3">
         <v>30</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1520,63 +1624,95 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+      <c r="AM7" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AN7" s="5">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="AO7" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP7" s="5">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="AQ7" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR7" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="AS7" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="AT7" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AU7" s="5">
+        <v>25</v>
+      </c>
+      <c r="AV7" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="3">
         <v>4</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="T8" s="3">
         <v>10</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1588,10 +1724,10 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
@@ -1599,58 +1735,88 @@
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
-    </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM8" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="AN8" s="5">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="AO8" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP8" s="5">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="AQ8" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR8" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="AT8" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="AU8" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AV8" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="3">
         <v>4</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="T9" s="3">
         <v>10</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1662,10 +1828,10 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1673,66 +1839,96 @@
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
-    </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="AN9" s="5">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="AO9" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP9" s="5">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="AQ9" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR9" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="AT9" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AU9" s="5">
+        <v>25</v>
+      </c>
+      <c r="AV9" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3">
         <v>20</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T10" s="3">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
@@ -1745,58 +1941,59 @@
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
-    </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM10" s="3"/>
+    </row>
+    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>340</v>
       </c>
       <c r="P11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>1</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T11" s="3">
         <v>10</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1815,58 +2012,59 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM11" s="3"/>
+    </row>
+    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>150</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q12" s="3">
         <v>96</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T12" s="3">
         <v>10</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1885,56 +2083,57 @@
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
-    </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM12" s="3"/>
+    </row>
+    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>10</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1953,56 +2152,57 @@
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
-    </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM13" s="3"/>
+    </row>
+    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3">
         <v>1000</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -2021,56 +2221,57 @@
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM14" s="3"/>
+    </row>
+    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3">
         <v>4</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -2089,58 +2290,59 @@
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM15" s="3"/>
+    </row>
+    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>0.49</v>
       </c>
       <c r="P16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T16" s="3">
         <v>10</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2159,58 +2361,59 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
-    </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM16" s="3"/>
+    </row>
+    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>0.25</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q17" s="3">
         <v>96</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T17" s="3">
         <v>10</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2229,56 +2432,57 @@
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
-    </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM17" s="3"/>
+    </row>
+    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>5</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2297,58 +2501,59 @@
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
-    </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM18" s="3"/>
+    </row>
+    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>16</v>
       </c>
       <c r="P19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>1</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T19" s="3">
         <v>10</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2367,58 +2572,59 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
-    </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM19" s="3"/>
+    </row>
+    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>11</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q20" s="3">
         <v>96</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T20" s="3">
         <v>10</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2437,58 +2643,59 @@
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
-    </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM20" s="3"/>
+    </row>
+    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3">
         <v>579</v>
       </c>
       <c r="P21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>1</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T21" s="3">
         <v>10</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2507,58 +2714,59 @@
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
-    </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM21" s="3"/>
+    </row>
+    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3">
         <v>27.7</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q22" s="3">
         <v>96</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T22" s="3">
         <v>10</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2577,58 +2785,59 @@
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
-    </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM22" s="3"/>
+    </row>
+    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>3.79</v>
       </c>
       <c r="P23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T23" s="3">
         <v>10</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2647,58 +2856,59 @@
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
-    </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM23" s="3"/>
+    </row>
+    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>2.85</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q24" s="3">
         <v>96</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T24" s="3">
         <v>10</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2717,56 +2927,57 @@
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
-    </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM24" s="3"/>
+    </row>
+    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>1300</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q25" s="3">
         <v>1</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2785,54 +2996,55 @@
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
-    </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM25" s="3"/>
+    </row>
+    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>15</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2851,56 +3063,57 @@
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM26" s="3"/>
+    </row>
+    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>32</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2919,56 +3132,57 @@
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
-    </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM27" s="3"/>
+    </row>
+    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>64</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T28" s="3">
         <v>10</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2987,68 +3201,69 @@
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
-    </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM28" s="3"/>
+    </row>
+    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>126</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q29" s="3">
         <v>30</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA29" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="AA29" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -3061,68 +3276,69 @@
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
-    </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM29" s="3"/>
+    </row>
+    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>252</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T30" s="3">
         <v>10</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA30" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="AA30" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
@@ -3135,68 +3351,69 @@
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
-    </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM30" s="3"/>
+    </row>
+    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>630</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Z31" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA31" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="AA31" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
@@ -3209,68 +3426,69 @@
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
-    </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM31" s="3"/>
+    </row>
+    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>1260</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T32" s="3">
         <v>10</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Z32" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA32" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="AA32" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
@@ -3283,68 +3501,69 @@
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
-    </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM32" s="3"/>
+    </row>
+    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3">
         <v>126</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q33" s="3">
         <v>30</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z33" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA33" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="AA33" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
@@ -3357,68 +3576,69 @@
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
-    </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM33" s="3"/>
+    </row>
+    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>252</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T34" s="3">
         <v>10</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA34" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="AA34" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
@@ -3431,56 +3651,57 @@
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
-    </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM34" s="3"/>
+    </row>
+    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>630</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q35" s="3">
         <v>30</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3499,56 +3720,57 @@
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
-    </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM35" s="3"/>
+    </row>
+    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>1260</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T36" s="3">
         <v>10</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3567,66 +3789,67 @@
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
-    </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM36" s="3"/>
+    </row>
+    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA37" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="AA37" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3639,68 +3862,69 @@
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
-    </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM37" s="3"/>
+    </row>
+    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>252</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z38" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA38" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="AA38" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3713,58 +3937,59 @@
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
-    </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM38" s="3"/>
+    </row>
+    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3">
         <v>1000</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q39" s="3">
         <v>96</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3783,58 +4008,59 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
-    </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM39" s="3"/>
+    </row>
+    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>13.98</v>
       </c>
       <c r="P40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>1</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T40" s="3">
         <v>10</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3853,58 +4079,59 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
-    </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM40" s="3"/>
+    </row>
+    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>0.54500000000000004</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T41" s="3">
         <v>10</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3923,56 +4150,57 @@
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
-    </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM41" s="3"/>
+    </row>
+    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>15</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3991,54 +4219,55 @@
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
-    </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM42" s="3"/>
+    </row>
+    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>8</v>
       </c>
       <c r="P43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>1</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S43" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q43" s="3">
-        <v>1</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -4057,58 +4286,59 @@
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
-    </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM43" s="3"/>
+    </row>
+    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>1.7</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q44" s="3">
         <v>96</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T44" s="3">
         <v>10</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -4127,58 +4357,59 @@
       <c r="AJ44" s="3"/>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
-    </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM44" s="3"/>
+    </row>
+    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>0.91</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T45" s="3">
         <v>10</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4197,56 +4428,57 @@
       <c r="AJ45" s="3"/>
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
-    </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM45" s="3"/>
+    </row>
+    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>0.05</v>
       </c>
       <c r="P46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>1</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S46" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q46" s="3">
-        <v>1</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4265,58 +4497,59 @@
       <c r="AJ46" s="3"/>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
-    </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM46" s="3"/>
+    </row>
+    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>145</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q47" s="3">
         <v>96</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T47" s="3">
         <v>10</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4335,58 +4568,59 @@
       <c r="AJ47" s="3"/>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
-    </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM47" s="3"/>
+    </row>
+    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>16.100000000000001</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q48" s="3">
         <v>96</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T48" s="3">
         <v>10</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4405,56 +4639,57 @@
       <c r="AJ48" s="3"/>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
-    </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM48" s="3"/>
+    </row>
+    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>100</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4473,54 +4708,55 @@
       <c r="AJ49" s="3"/>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
-    </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM49" s="3"/>
+    </row>
+    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>1</v>
       </c>
       <c r="P50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>1</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="Q50" s="3">
-        <v>1</v>
-      </c>
-      <c r="R50" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4539,54 +4775,55 @@
       <c r="AJ50" s="3"/>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
-    </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM50" s="3"/>
+    </row>
+    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>10</v>
       </c>
       <c r="P51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>1</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T51" s="3">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="Q51" s="3">
-        <v>1</v>
-      </c>
-      <c r="R51" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4605,58 +4842,59 @@
       <c r="AJ51" s="3"/>
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
-    </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM51" s="3"/>
+    </row>
+    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N52" s="3">
         <v>6.5</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4675,58 +4913,59 @@
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
-    </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM52" s="3"/>
+    </row>
+    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N53" s="3">
         <v>9.5</v>
       </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q53" s="3">
         <v>7</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4745,58 +4984,59 @@
       <c r="AJ53" s="3"/>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
-    </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM53" s="3"/>
+    </row>
+    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N54" s="3">
         <v>5</v>
       </c>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q54" s="3">
         <v>7</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4815,58 +5055,59 @@
       <c r="AJ54" s="3"/>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
-    </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM54" s="3"/>
+    </row>
+    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N55" s="3">
         <v>8</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>1</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T55" s="3">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="Q55" s="3">
-        <v>1</v>
-      </c>
-      <c r="R55" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T55" s="3">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4885,58 +5126,59 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
-    </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM55" s="3"/>
+    </row>
+    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E56" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N56" s="3">
         <v>4</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>1</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T56" s="3">
+        <v>1</v>
+      </c>
+      <c r="U56" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="Q56" s="3">
-        <v>1</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T56" s="3">
-        <v>1</v>
-      </c>
-      <c r="U56" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4955,58 +5197,59 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
-    </row>
-    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM56" s="3"/>
+    </row>
+    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N57" s="3">
         <v>5.5</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q57" s="3">
         <v>30</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -5025,70 +5268,71 @@
       <c r="AJ57" s="3"/>
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
-    </row>
-    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM57" s="3"/>
+    </row>
+    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N58" s="3">
         <v>6</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q58" s="3">
         <v>7</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Z58" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AA58" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
@@ -5101,70 +5345,71 @@
       <c r="AJ58" s="3"/>
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
-    </row>
-    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM58" s="3"/>
+    </row>
+    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N59" s="3">
         <v>6</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q59" s="3">
         <v>7</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z59" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AA59" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
@@ -5177,58 +5422,59 @@
       <c r="AJ59" s="3"/>
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
-    </row>
-    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM59" s="3"/>
+    </row>
+    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N60" s="3">
         <v>4</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q60" s="3">
         <v>7</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
@@ -5247,70 +5493,71 @@
       <c r="AJ60" s="3"/>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
-    </row>
-    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM60" s="3"/>
+    </row>
+    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E61" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N61" s="3">
         <v>5</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>1</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T61" s="3">
+        <v>1</v>
+      </c>
+      <c r="U61" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>1</v>
-      </c>
-      <c r="R61" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S61" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T61" s="3">
-        <v>1</v>
-      </c>
-      <c r="U61" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Z61" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AA61" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
@@ -5323,70 +5570,71 @@
       <c r="AJ61" s="3"/>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
-    </row>
-    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM61" s="3"/>
+    </row>
+    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N62" s="3">
         <v>5</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T62" s="3">
+        <v>1</v>
+      </c>
+      <c r="U62" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z62" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AA62" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
@@ -5399,58 +5647,59 @@
       <c r="AJ62" s="3"/>
       <c r="AK62" s="3"/>
       <c r="AL62" s="3"/>
-    </row>
-    <row r="63" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM62" s="3"/>
+    </row>
+    <row r="63" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E63" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N63" s="3">
         <v>3</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>1</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T63" s="3">
+        <v>1</v>
+      </c>
+      <c r="U63" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="Q63" s="3">
-        <v>1</v>
-      </c>
-      <c r="R63" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S63" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T63" s="3">
-        <v>1</v>
-      </c>
-      <c r="U63" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
@@ -5469,70 +5718,71 @@
       <c r="AJ63" s="3"/>
       <c r="AK63" s="3"/>
       <c r="AL63" s="3"/>
-    </row>
-    <row r="64" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM63" s="3"/>
+    </row>
+    <row r="64" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E64" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N64" s="3"/>
       <c r="O64" s="3">
         <v>2</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T64" s="3">
         <v>1</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z64" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA64" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
@@ -5545,70 +5795,71 @@
       <c r="AJ64" s="3"/>
       <c r="AK64" s="3"/>
       <c r="AL64" s="3"/>
-    </row>
-    <row r="65" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM64" s="3"/>
+    </row>
+    <row r="65" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E65" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" s="3">
         <v>2</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T65" s="3">
         <v>1</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z65" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA65" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
@@ -5621,70 +5872,71 @@
       <c r="AJ65" s="3"/>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3"/>
-    </row>
-    <row r="66" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM65" s="3"/>
+    </row>
+    <row r="66" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E66" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3">
         <v>1</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T66" s="3">
         <v>1</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z66" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA66" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
@@ -5697,70 +5949,71 @@
       <c r="AJ66" s="3"/>
       <c r="AK66" s="3"/>
       <c r="AL66" s="3"/>
-    </row>
-    <row r="67" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM66" s="3"/>
+    </row>
+    <row r="67" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E67" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3">
         <v>1</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T67" s="3">
         <v>1</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z67" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AA67" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
@@ -5773,58 +6026,59 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
-    </row>
-    <row r="68" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM67" s="3"/>
+    </row>
+    <row r="68" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3">
         <v>20</v>
       </c>
       <c r="P68" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>1</v>
+      </c>
+      <c r="R68" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S68" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q68" s="3">
-        <v>1</v>
-      </c>
-      <c r="R68" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T68" s="3">
         <v>10</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
@@ -5843,58 +6097,59 @@
       <c r="AJ68" s="3"/>
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
-    </row>
-    <row r="69" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM68" s="3"/>
+    </row>
+    <row r="69" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3">
         <v>5</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q69" s="3">
         <v>96</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T69" s="3">
         <v>10</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
@@ -5913,56 +6168,57 @@
       <c r="AJ69" s="3"/>
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
-    </row>
-    <row r="70" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM69" s="3"/>
+    </row>
+    <row r="70" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="3">
         <v>50</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q70" s="3">
         <v>1</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T70" s="3">
         <v>1</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -5981,58 +6237,59 @@
       <c r="AJ70" s="3"/>
       <c r="AK70" s="3"/>
       <c r="AL70" s="3"/>
-    </row>
-    <row r="71" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM70" s="3"/>
+    </row>
+    <row r="71" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E71" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3">
         <v>0.374</v>
       </c>
       <c r="P71" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>1</v>
+      </c>
+      <c r="R71" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S71" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q71" s="3">
-        <v>1</v>
-      </c>
-      <c r="R71" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="T71" s="3">
         <v>1</v>
       </c>
       <c r="U71" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6051,56 +6308,57 @@
       <c r="AJ71" s="3"/>
       <c r="AK71" s="3"/>
       <c r="AL71" s="3"/>
-    </row>
-    <row r="72" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM71" s="3"/>
+    </row>
+    <row r="72" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="3">
         <v>100</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q72" s="3">
         <v>1</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T72" s="3">
         <v>1</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
@@ -6119,56 +6377,57 @@
       <c r="AJ72" s="3"/>
       <c r="AK72" s="3"/>
       <c r="AL72" s="3"/>
-    </row>
-    <row r="73" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM72" s="3"/>
+    </row>
+    <row r="73" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N73" s="3"/>
       <c r="O73" s="3">
         <v>4000</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q73" s="3">
         <v>1</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T73" s="3">
         <v>1</v>
       </c>
       <c r="U73" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
@@ -6187,56 +6446,57 @@
       <c r="AJ73" s="3"/>
       <c r="AK73" s="3"/>
       <c r="AL73" s="3"/>
-    </row>
-    <row r="74" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM73" s="3"/>
+    </row>
+    <row r="74" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="3">
         <v>0.24</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q74" s="3">
         <v>1</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T74" s="3">
         <v>1</v>
       </c>
       <c r="U74" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
@@ -6255,56 +6515,57 @@
       <c r="AJ74" s="3"/>
       <c r="AK74" s="3"/>
       <c r="AL74" s="3"/>
-    </row>
-    <row r="75" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM74" s="3"/>
+    </row>
+    <row r="75" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" s="3">
         <v>30</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T75" s="3">
         <v>1</v>
       </c>
       <c r="U75" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
@@ -6323,58 +6584,59 @@
       <c r="AJ75" s="3"/>
       <c r="AK75" s="3"/>
       <c r="AL75" s="3"/>
-    </row>
-    <row r="76" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM75" s="3"/>
+    </row>
+    <row r="76" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E76" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" s="3">
         <v>37</v>
       </c>
       <c r="P76" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>1</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>1</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T76" s="3">
         <v>10</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
@@ -6393,58 +6655,59 @@
       <c r="AJ76" s="3"/>
       <c r="AK76" s="3"/>
       <c r="AL76" s="3"/>
-    </row>
-    <row r="77" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM76" s="3"/>
+    </row>
+    <row r="77" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E77" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N77" s="3"/>
       <c r="O77" s="3">
         <v>37</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q77" s="3">
         <v>96</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T77" s="3">
         <v>10</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
@@ -6463,56 +6726,57 @@
       <c r="AJ77" s="3"/>
       <c r="AK77" s="3"/>
       <c r="AL77" s="3"/>
-    </row>
-    <row r="78" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM77" s="3"/>
+    </row>
+    <row r="78" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" s="3">
         <v>7400</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q78" s="3">
         <v>1</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T78" s="3">
         <v>1</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>
@@ -6531,6 +6795,7 @@
       <c r="AJ78" s="3"/>
       <c r="AK78" s="3"/>
       <c r="AL78" s="3"/>
+      <c r="AM78" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/inst/extdata/montana_criteria_crosswalk.xlsx
+++ b/inst/extdata/montana_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{A9EF67AA-C36E-4079-ADCD-13CFFD121107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894F2CA2-1D0E-4B1B-A280-E513EFBD4E09}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{A9EF67AA-C36E-4079-ADCD-13CFFD121107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6C33F9B-4F32-4CFE-9D1C-1232DD2016B9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="177">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -530,9 +530,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>MinEqMagnitude</t>
   </si>
   <si>
@@ -554,10 +551,22 @@
     <t>pH_param_9</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Min Multiplier</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -979,22 +988,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C39393-A058-421C-ACEB-02156F4251A2}">
-  <dimension ref="A1:AX78"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BA78"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="24" width="9.140625" style="5"/>
-    <col min="25" max="25" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="9.140625" style="5"/>
-    <col min="31" max="31" width="25.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="110.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="24" width="9.109375" style="5"/>
+    <col min="25" max="25" width="18.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="9.109375" style="5"/>
+    <col min="31" max="31" width="25.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="110.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.88671875" style="5" bestFit="1" customWidth="1"/>
     <col min="35" max="36" width="20" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="5"/>
+    <col min="37" max="38" width="10.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1119,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1125,28 +1134,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="AV1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AW1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="BA1" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="AX1" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1217,7 +1235,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1288,7 +1306,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1375,7 +1393,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1462,7 +1480,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1532,7 +1550,7 @@
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
       <c r="AM6" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AN6" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1562,7 +1580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1632,7 +1650,7 @@
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
       <c r="AM7" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AN7" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1662,7 +1680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1736,7 +1754,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AN8" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1766,7 +1784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1840,7 +1858,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AN9" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1870,7 +1888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1943,7 +1961,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -2014,7 +2032,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -2085,7 +2103,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -2154,7 +2172,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2223,7 +2241,7 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2292,7 +2310,7 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2363,7 +2381,7 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2434,7 +2452,7 @@
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2503,7 +2521,7 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -2574,7 +2592,7 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -2645,7 +2663,7 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
     </row>
-    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2716,7 +2734,7 @@
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
     </row>
-    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -2787,7 +2805,7 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -2858,7 +2876,7 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -2929,7 +2947,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -2998,7 +3016,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -3065,7 +3083,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -3134,7 +3152,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -3203,7 +3221,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3278,7 +3296,7 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
     </row>
-    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3353,7 +3371,7 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
     </row>
-    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3428,7 +3446,7 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
     </row>
-    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3503,7 +3521,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
     </row>
-    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3578,7 +3596,7 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
     </row>
-    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -3653,7 +3671,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
     </row>
-    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -3722,7 +3740,7 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -3791,7 +3809,7 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -3864,7 +3882,7 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -3939,7 +3957,7 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -4010,7 +4028,7 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -4081,7 +4099,7 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -4152,7 +4170,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -4221,7 +4239,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4288,7 +4306,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4359,7 +4377,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4430,7 +4448,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4499,7 +4517,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4570,7 +4588,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4641,7 +4659,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -4710,7 +4728,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -4777,7 +4795,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -4844,7 +4862,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -4915,7 +4933,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -4986,7 +5004,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -5057,7 +5075,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -5128,7 +5146,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -5199,7 +5217,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -5270,7 +5288,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -5347,7 +5365,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
     </row>
-    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -5424,7 +5442,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
     </row>
-    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -5495,7 +5513,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
     </row>
-    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -5572,7 +5590,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
     </row>
-    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -5649,7 +5667,7 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
     </row>
-    <row r="63" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -5720,7 +5738,7 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
     </row>
-    <row r="64" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -5797,7 +5815,7 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
     </row>
-    <row r="65" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -5874,7 +5892,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
     </row>
-    <row r="66" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -5951,7 +5969,7 @@
       <c r="AL66" s="3"/>
       <c r="AM66" s="3"/>
     </row>
-    <row r="67" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -6028,7 +6046,7 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -6099,7 +6117,7 @@
       <c r="AL68" s="3"/>
       <c r="AM68" s="3"/>
     </row>
-    <row r="69" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -6170,7 +6188,7 @@
       <c r="AL69" s="3"/>
       <c r="AM69" s="3"/>
     </row>
-    <row r="70" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>39</v>
@@ -6239,7 +6257,7 @@
       <c r="AL70" s="3"/>
       <c r="AM70" s="3"/>
     </row>
-    <row r="71" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>39</v>
@@ -6310,7 +6328,7 @@
       <c r="AL71" s="3"/>
       <c r="AM71" s="3"/>
     </row>
-    <row r="72" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>39</v>
@@ -6379,7 +6397,7 @@
       <c r="AL72" s="3"/>
       <c r="AM72" s="3"/>
     </row>
-    <row r="73" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>39</v>
@@ -6448,7 +6466,7 @@
       <c r="AL73" s="3"/>
       <c r="AM73" s="3"/>
     </row>
-    <row r="74" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>39</v>
@@ -6517,7 +6535,7 @@
       <c r="AL74" s="3"/>
       <c r="AM74" s="3"/>
     </row>
-    <row r="75" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>39</v>
@@ -6586,7 +6604,7 @@
       <c r="AL75" s="3"/>
       <c r="AM75" s="3"/>
     </row>
-    <row r="76" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>39</v>
@@ -6657,7 +6675,7 @@
       <c r="AL76" s="3"/>
       <c r="AM76" s="3"/>
     </row>
-    <row r="77" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>39</v>
@@ -6728,7 +6746,7 @@
       <c r="AL77" s="3"/>
       <c r="AM77" s="3"/>
     </row>
-    <row r="78" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>39</v>

--- a/inst/extdata/montana_criteria_crosswalk.xlsx
+++ b/inst/extdata/montana_criteria_crosswalk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{A9EF67AA-C36E-4079-ADCD-13CFFD121107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6C33F9B-4F32-4CFE-9D1C-1232DD2016B9}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{A9EF67AA-C36E-4079-ADCD-13CFFD121107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9692D22-3F7B-45B4-BB92-22388320D62F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A45B80D3-8FBF-4866-A675-36E913F18D91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="171">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -101,18 +101,12 @@
     <t>FreqMethod</t>
   </si>
   <si>
-    <t>AssessPeriod</t>
-  </si>
-  <si>
     <t>AssessPeriodStartDate</t>
   </si>
   <si>
     <t>AssessPeriodEndDate</t>
   </si>
   <si>
-    <t>Season</t>
-  </si>
-  <si>
     <t>SeasonStartDate</t>
   </si>
   <si>
@@ -461,24 +455,6 @@
     <t>Jul 1</t>
   </si>
   <si>
-    <t>Jun-Sep</t>
-  </si>
-  <si>
-    <t>Apr-Oct</t>
-  </si>
-  <si>
-    <t>Nov-Mar</t>
-  </si>
-  <si>
-    <t>Mar-Aug</t>
-  </si>
-  <si>
-    <t>Feb-Aug</t>
-  </si>
-  <si>
-    <t>Jul-Sep</t>
-  </si>
-  <si>
     <t>Salmonid fish present</t>
   </si>
   <si>
@@ -567,6 +543,12 @@
   </si>
   <si>
     <t>Max Exponent</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Links</t>
   </si>
 </sst>
 </file>
@@ -991,9 +973,7 @@
   <dimension ref="A1:BA78"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="24" width="9.109375" style="5"/>
-    <col min="25" max="25" width="18.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="9.109375" style="5"/>
+    <col min="1" max="30" width="9.109375" style="5"/>
     <col min="31" max="31" width="25.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="110.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
@@ -1089,139 +1069,139 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AY1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="AZ1" s="6" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="BA1" s="6" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>750</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T2" s="3">
         <v>10</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
@@ -1238,61 +1218,61 @@
     <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>87</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q3" s="3">
         <v>96</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T3" s="3">
         <v>10</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -1309,69 +1289,69 @@
     <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T4" s="3">
         <v>10</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
@@ -1396,69 +1376,69 @@
     <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T5" s="3">
         <v>10</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
@@ -1483,74 +1463,74 @@
     <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q6" s="3">
         <v>30</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T6" s="3">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
       <c r="AM6" s="5" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AN6" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1583,74 +1563,74 @@
     <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q7" s="3">
         <v>30</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
       <c r="AM7" s="5" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AN7" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1683,69 +1663,69 @@
     <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q8" s="3">
         <v>4</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="T8" s="3">
         <v>10</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
@@ -1754,7 +1734,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AN8" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1787,69 +1767,69 @@
     <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q9" s="3">
         <v>4</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="T9" s="3">
         <v>10</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1858,7 +1838,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AN9" s="5">
         <v>5.7700000000000001E-2</v>
@@ -1891,63 +1871,61 @@
     <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3">
         <v>20</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T10" s="3">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="Z10" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="X10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -1964,61 +1942,61 @@
     <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>340</v>
       </c>
       <c r="P11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>1</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T11" s="3">
         <v>10</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2035,61 +2013,61 @@
     <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>150</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q12" s="3">
         <v>96</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T12" s="3">
         <v>10</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2106,59 +2084,59 @@
     <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>10</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -2175,59 +2153,59 @@
     <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3">
         <v>1000</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2244,59 +2222,59 @@
     <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3">
         <v>4</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2313,61 +2291,61 @@
     <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>0.49</v>
       </c>
       <c r="P16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T16" s="3">
         <v>10</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2384,61 +2362,61 @@
     <row r="17" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>0.25</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q17" s="3">
         <v>96</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T17" s="3">
         <v>10</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -2455,59 +2433,59 @@
     <row r="18" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>5</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2524,61 +2502,61 @@
     <row r="19" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>16</v>
       </c>
       <c r="P19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>1</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T19" s="3">
         <v>10</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -2595,61 +2573,61 @@
     <row r="20" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>11</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q20" s="3">
         <v>96</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T20" s="3">
         <v>10</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2666,61 +2644,61 @@
     <row r="21" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3">
         <v>579</v>
       </c>
       <c r="P21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>1</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T21" s="3">
         <v>10</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -2737,61 +2715,61 @@
     <row r="22" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3">
         <v>27.7</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="3">
         <v>96</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T22" s="3">
         <v>10</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
@@ -2808,61 +2786,61 @@
     <row r="23" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>3.79</v>
       </c>
       <c r="P23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T23" s="3">
         <v>10</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -2879,61 +2857,61 @@
     <row r="24" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>2.85</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q24" s="3">
         <v>96</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T24" s="3">
         <v>10</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -2950,59 +2928,59 @@
     <row r="25" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>1300</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q25" s="3">
         <v>1</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -3019,57 +2997,57 @@
     <row r="26" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>15</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -3086,59 +3064,59 @@
     <row r="27" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>32</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -3155,59 +3133,59 @@
     <row r="28" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>64</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T28" s="3">
         <v>10</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -3224,65 +3202,63 @@
     <row r="29" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>126</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q29" s="3">
         <v>30</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z29" s="4" t="s">
+      <c r="X29" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y29" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AA29" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -3299,65 +3275,63 @@
     <row r="30" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>252</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T30" s="3">
         <v>10</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z30" s="4" t="s">
+      <c r="X30" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y30" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AA30" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3374,65 +3348,63 @@
     <row r="31" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>630</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z31" s="4" t="s">
+      <c r="X31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y31" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AA31" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3449,65 +3421,63 @@
     <row r="32" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>1260</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T32" s="3">
         <v>10</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z32" s="4" t="s">
+      <c r="X32" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y32" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AA32" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3524,65 +3494,63 @@
     <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3">
         <v>126</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q33" s="3">
         <v>30</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z33" s="4" t="s">
+      <c r="X33" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AA33" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -3599,65 +3567,63 @@
     <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>252</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T34" s="3">
         <v>10</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z34" s="4" t="s">
+      <c r="X34" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y34" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AA34" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -3674,59 +3640,59 @@
     <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>630</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q35" s="3">
         <v>30</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3743,59 +3709,59 @@
     <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>1260</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T36" s="3">
         <v>10</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3812,63 +3778,61 @@
     <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z37" s="4" t="s">
+      <c r="X37" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y37" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AA37" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3885,65 +3849,63 @@
     <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>252</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z38" s="4" t="s">
+      <c r="X38" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AA38" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
@@ -3960,61 +3922,61 @@
     <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3">
         <v>1000</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q39" s="3">
         <v>96</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -4031,61 +3993,61 @@
     <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>13.98</v>
       </c>
       <c r="P40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>1</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T40" s="3">
         <v>10</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
@@ -4102,61 +4064,61 @@
     <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>0.54500000000000004</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q41" s="3">
         <v>1</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T41" s="3">
         <v>10</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
@@ -4173,59 +4135,59 @@
     <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>15</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -4242,57 +4204,57 @@
     <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>8</v>
       </c>
       <c r="P43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>1</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q43" s="3">
-        <v>1</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
@@ -4309,61 +4271,61 @@
     <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>1.7</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q44" s="3">
         <v>96</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T44" s="3">
         <v>10</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
@@ -4380,61 +4342,61 @@
     <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>0.91</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T45" s="3">
         <v>10</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -4451,59 +4413,59 @@
     <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>0.05</v>
       </c>
       <c r="P46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>1</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q46" s="3">
-        <v>1</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -4520,61 +4482,61 @@
     <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>145</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q47" s="3">
         <v>96</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T47" s="3">
         <v>10</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -4591,61 +4553,61 @@
     <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>16.100000000000001</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q48" s="3">
         <v>96</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T48" s="3">
         <v>10</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -4662,59 +4624,59 @@
     <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>100</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
@@ -4731,57 +4693,57 @@
     <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>1</v>
       </c>
       <c r="P50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>1</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Q50" s="3">
-        <v>1</v>
-      </c>
-      <c r="R50" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
@@ -4798,57 +4760,57 @@
     <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>10</v>
       </c>
       <c r="P51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>1</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="T51" s="3">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Q51" s="3">
-        <v>1</v>
-      </c>
-      <c r="R51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
@@ -4865,61 +4827,61 @@
     <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N52" s="3">
         <v>6.5</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -4936,61 +4898,61 @@
     <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N53" s="3">
         <v>9.5</v>
       </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q53" s="3">
         <v>7</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -5007,61 +4969,61 @@
     <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N54" s="3">
         <v>5</v>
       </c>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q54" s="3">
         <v>7</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -5078,61 +5040,61 @@
     <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N55" s="3">
         <v>8</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>1</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T55" s="3">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Q55" s="3">
-        <v>1</v>
-      </c>
-      <c r="R55" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T55" s="3">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
@@ -5149,61 +5111,61 @@
     <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E56" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N56" s="3">
         <v>4</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>1</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T56" s="3">
+        <v>1</v>
+      </c>
+      <c r="U56" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Q56" s="3">
-        <v>1</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T56" s="3">
-        <v>1</v>
-      </c>
-      <c r="U56" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
@@ -5220,61 +5182,61 @@
     <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N57" s="3">
         <v>5.5</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q57" s="3">
         <v>30</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
       <c r="AB57" s="3"/>
       <c r="AC57" s="3"/>
       <c r="AD57" s="3"/>
@@ -5291,67 +5253,65 @@
     <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N58" s="3">
         <v>6</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q58" s="3">
         <v>7</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z58" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA58" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="X58" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y58" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
       <c r="AD58" s="3"/>
@@ -5368,67 +5328,65 @@
     <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N59" s="3">
         <v>6</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q59" s="3">
         <v>7</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z59" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA59" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="X59" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y59" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
       <c r="AD59" s="3"/>
@@ -5445,61 +5403,61 @@
     <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N60" s="3">
         <v>4</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q60" s="3">
         <v>7</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="4"/>
-      <c r="AA60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
       <c r="AB60" s="3"/>
       <c r="AC60" s="3"/>
       <c r="AD60" s="3"/>
@@ -5516,67 +5474,65 @@
     <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E61" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N61" s="3">
         <v>5</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>1</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T61" s="3">
+        <v>1</v>
+      </c>
+      <c r="U61" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>1</v>
-      </c>
-      <c r="R61" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S61" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T61" s="3">
-        <v>1</v>
-      </c>
-      <c r="U61" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z61" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA61" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="X61" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y61" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
       <c r="AD61" s="3"/>
@@ -5593,67 +5549,65 @@
     <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N62" s="3">
         <v>5</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T62" s="3">
+        <v>1</v>
+      </c>
+      <c r="U62" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z62" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA62" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="X62" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y62" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
       <c r="AD62" s="3"/>
@@ -5670,61 +5624,61 @@
     <row r="63" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E63" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N63" s="3">
         <v>3</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>1</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T63" s="3">
+        <v>1</v>
+      </c>
+      <c r="U63" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Q63" s="3">
-        <v>1</v>
-      </c>
-      <c r="R63" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S63" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T63" s="3">
-        <v>1</v>
-      </c>
-      <c r="U63" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
       <c r="AB63" s="3"/>
       <c r="AC63" s="3"/>
       <c r="AD63" s="3"/>
@@ -5741,67 +5695,65 @@
     <row r="64" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E64" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N64" s="3"/>
       <c r="O64" s="3">
         <v>2</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T64" s="3">
         <v>1</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z64" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA64" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="X64" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y64" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
       <c r="AD64" s="3"/>
@@ -5818,67 +5770,65 @@
     <row r="65" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E65" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" s="3">
         <v>2</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T65" s="3">
         <v>1</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z65" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA65" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="X65" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y65" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
       <c r="AD65" s="3"/>
@@ -5895,67 +5845,65 @@
     <row r="66" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E66" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3">
         <v>1</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T66" s="3">
         <v>1</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z66" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA66" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="X66" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y66" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
@@ -5972,67 +5920,65 @@
     <row r="67" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E67" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3">
         <v>1</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T67" s="3">
         <v>1</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z67" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA67" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="X67" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y67" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
@@ -6049,61 +5995,61 @@
     <row r="68" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3">
         <v>20</v>
       </c>
       <c r="P68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>1</v>
+      </c>
+      <c r="R68" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S68" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q68" s="3">
-        <v>1</v>
-      </c>
-      <c r="R68" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T68" s="3">
         <v>10</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
       <c r="AB68" s="3"/>
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
@@ -6120,61 +6066,61 @@
     <row r="69" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3">
         <v>5</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q69" s="3">
         <v>96</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T69" s="3">
         <v>10</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
       <c r="AB69" s="3"/>
       <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
@@ -6191,59 +6137,59 @@
     <row r="70" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="3">
         <v>50</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q70" s="3">
         <v>1</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T70" s="3">
         <v>1</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="4"/>
-      <c r="AA70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
       <c r="AB70" s="3"/>
       <c r="AC70" s="3"/>
       <c r="AD70" s="3"/>
@@ -6260,61 +6206,61 @@
     <row r="71" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E71" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3">
         <v>0.374</v>
       </c>
       <c r="P71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>1</v>
+      </c>
+      <c r="R71" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S71" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q71" s="3">
-        <v>1</v>
-      </c>
-      <c r="R71" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="T71" s="3">
         <v>1</v>
       </c>
       <c r="U71" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="4"/>
-      <c r="AA71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="3"/>
+      <c r="AA71" s="3"/>
       <c r="AB71" s="3"/>
       <c r="AC71" s="3"/>
       <c r="AD71" s="3"/>
@@ -6331,59 +6277,59 @@
     <row r="72" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="3">
         <v>100</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q72" s="3">
         <v>1</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T72" s="3">
         <v>1</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="4"/>
-      <c r="AA72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
       <c r="AB72" s="3"/>
       <c r="AC72" s="3"/>
       <c r="AD72" s="3"/>
@@ -6400,59 +6346,59 @@
     <row r="73" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N73" s="3"/>
       <c r="O73" s="3">
         <v>4000</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q73" s="3">
         <v>1</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T73" s="3">
         <v>1</v>
       </c>
       <c r="U73" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="4"/>
-      <c r="AA73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="3"/>
+      <c r="AA73" s="3"/>
       <c r="AB73" s="3"/>
       <c r="AC73" s="3"/>
       <c r="AD73" s="3"/>
@@ -6469,59 +6415,59 @@
     <row r="74" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="3">
         <v>0.24</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q74" s="3">
         <v>1</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T74" s="3">
         <v>1</v>
       </c>
       <c r="U74" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="4"/>
-      <c r="AA74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
       <c r="AB74" s="3"/>
       <c r="AC74" s="3"/>
       <c r="AD74" s="3"/>
@@ -6538,59 +6484,59 @@
     <row r="75" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" s="3">
         <v>30</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q75" s="3">
         <v>1</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T75" s="3">
         <v>1</v>
       </c>
       <c r="U75" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="4"/>
-      <c r="AA75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="3"/>
+      <c r="AA75" s="3"/>
       <c r="AB75" s="3"/>
       <c r="AC75" s="3"/>
       <c r="AD75" s="3"/>
@@ -6607,61 +6553,61 @@
     <row r="76" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E76" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" s="3">
         <v>37</v>
       </c>
       <c r="P76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>1</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>1</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="T76" s="3">
         <v>10</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="4"/>
-      <c r="AA76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
       <c r="AB76" s="3"/>
       <c r="AC76" s="3"/>
       <c r="AD76" s="3"/>
@@ -6678,61 +6624,61 @@
     <row r="77" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E77" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N77" s="3"/>
       <c r="O77" s="3">
         <v>37</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q77" s="3">
         <v>96</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T77" s="3">
         <v>10</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="4"/>
-      <c r="AA77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="3"/>
+      <c r="AA77" s="3"/>
       <c r="AB77" s="3"/>
       <c r="AC77" s="3"/>
       <c r="AD77" s="3"/>
@@ -6749,52 +6695,52 @@
     <row r="78" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" s="3">
         <v>7400</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q78" s="3">
         <v>1</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T78" s="3">
         <v>1</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>
